--- a/wwwroot/55/BoxBreakingReport.xlsx
+++ b/wwwroot/55/BoxBreakingReport.xlsx
@@ -95,7 +95,7 @@
     <t>1001</t>
   </si>
   <si>
-    <t>22960-22979</t>
+    <t>122961-122980</t>
   </si>
   <si>
     <t>5009</t>
@@ -113,19 +113,19 @@
     <t/>
   </si>
   <si>
-    <t>940-959</t>
+    <t>100941-100960</t>
   </si>
   <si>
     <t>5120</t>
   </si>
   <si>
-    <t>2760-2779</t>
+    <t>102761-102780</t>
   </si>
   <si>
     <t>6015</t>
   </si>
   <si>
-    <t>4460-4479</t>
+    <t>104461-104480</t>
   </si>
   <si>
     <t>6045</t>
@@ -134,49 +134,49 @@
     <t>1 to 3</t>
   </si>
   <si>
-    <t>6540-6599</t>
+    <t>106541-106600</t>
   </si>
   <si>
     <t>9125</t>
   </si>
   <si>
-    <t>16820-16839</t>
+    <t>116821-116840</t>
   </si>
   <si>
     <t>9129</t>
   </si>
   <si>
-    <t>17580-17599</t>
+    <t>117581-117600</t>
   </si>
   <si>
     <t>9134</t>
   </si>
   <si>
-    <t>17720-17739</t>
+    <t>117721-117740</t>
   </si>
   <si>
     <t>9140</t>
   </si>
   <si>
-    <t>18480-18499</t>
+    <t>118481-118500</t>
   </si>
   <si>
     <t>9146</t>
   </si>
   <si>
-    <t>20000-20019</t>
+    <t>120001-120020</t>
   </si>
   <si>
     <t>9151</t>
   </si>
   <si>
-    <t>21380-21399</t>
+    <t>121381-121400</t>
   </si>
   <si>
     <t>9159</t>
   </si>
   <si>
-    <t>21660-21679</t>
+    <t>121661-121680</t>
   </si>
   <si>
     <t>1253</t>
@@ -188,25 +188,25 @@
     <t>1003</t>
   </si>
   <si>
-    <t>0-19</t>
+    <t>100001-100020</t>
   </si>
   <si>
     <t>5076</t>
   </si>
   <si>
-    <t>1560-1579</t>
+    <t>101561-101580</t>
   </si>
   <si>
     <t>5121</t>
   </si>
   <si>
-    <t>3140-3159</t>
+    <t>103141-103160</t>
   </si>
   <si>
     <t>5143</t>
   </si>
   <si>
-    <t>4180-4199</t>
+    <t>104181-104200</t>
   </si>
   <si>
     <t>6070</t>
@@ -215,49 +215,49 @@
     <t>1 to 2</t>
   </si>
   <si>
-    <t>7940-7979</t>
+    <t>107941-107980</t>
   </si>
   <si>
     <t>6138</t>
   </si>
   <si>
-    <t>8600-8619</t>
+    <t>108601-108620</t>
   </si>
   <si>
     <t>9003</t>
   </si>
   <si>
-    <t>9020-9039</t>
+    <t>109021-109040</t>
   </si>
   <si>
     <t>9009</t>
   </si>
   <si>
-    <t>9660-9679</t>
+    <t>109661-109680</t>
   </si>
   <si>
     <t>9015</t>
   </si>
   <si>
-    <t>10800-10819</t>
+    <t>110801-110820</t>
   </si>
   <si>
     <t>9060</t>
   </si>
   <si>
-    <t>13480-13499</t>
+    <t>113481-113500</t>
   </si>
   <si>
     <t>9064</t>
   </si>
   <si>
-    <t>14600-14619</t>
+    <t>114601-114620</t>
   </si>
   <si>
     <t>9086</t>
   </si>
   <si>
-    <t>15120-15139</t>
+    <t>115121-115140</t>
   </si>
   <si>
     <t>2150</t>
@@ -269,61 +269,61 @@
     <t>1004</t>
   </si>
   <si>
-    <t>540-559</t>
+    <t>100541-100560</t>
   </si>
   <si>
     <t>5115</t>
   </si>
   <si>
-    <t>2620-2639</t>
+    <t>102621-102640</t>
   </si>
   <si>
     <t>5146</t>
   </si>
   <si>
-    <t>4320-4339</t>
+    <t>104321-104340</t>
   </si>
   <si>
     <t>6034</t>
   </si>
   <si>
-    <t>5080-5119</t>
+    <t>105081-105120</t>
   </si>
   <si>
     <t>6140</t>
   </si>
   <si>
-    <t>8740-8759</t>
+    <t>108741-108760</t>
   </si>
   <si>
     <t>9021</t>
   </si>
   <si>
-    <t>11940-11959</t>
+    <t>111941-111960</t>
   </si>
   <si>
     <t>9022</t>
   </si>
   <si>
-    <t>12440-12459</t>
+    <t>112441-112460</t>
   </si>
   <si>
     <t>9032</t>
   </si>
   <si>
-    <t>12700-12719</t>
+    <t>112701-112720</t>
   </si>
   <si>
     <t>9092</t>
   </si>
   <si>
-    <t>16140-16159</t>
+    <t>116141-116160</t>
   </si>
   <si>
     <t>9171</t>
   </si>
   <si>
-    <t>22440-22459</t>
+    <t>122441-122460</t>
   </si>
   <si>
     <t>6035</t>
@@ -335,61 +335,61 @@
     <t>1005</t>
   </si>
   <si>
-    <t>5880-5899</t>
+    <t>105881-105900</t>
   </si>
   <si>
     <t>6063</t>
   </si>
   <si>
-    <t>7280-7299</t>
+    <t>107281-107300</t>
   </si>
   <si>
     <t>6142</t>
   </si>
   <si>
-    <t>8880-8899</t>
+    <t>108881-108900</t>
   </si>
   <si>
     <t>9126</t>
   </si>
   <si>
-    <t>17200-17219</t>
+    <t>117201-117220</t>
   </si>
   <si>
     <t>9135</t>
   </si>
   <si>
-    <t>18100-18119</t>
+    <t>118101-118120</t>
   </si>
   <si>
     <t>9141</t>
   </si>
   <si>
-    <t>18980-18999</t>
+    <t>118981-119000</t>
   </si>
   <si>
     <t>9142</t>
   </si>
   <si>
-    <t>19240-19259</t>
+    <t>119241-119260</t>
   </si>
   <si>
     <t>9147</t>
   </si>
   <si>
-    <t>20500-20519</t>
+    <t>120501-120520</t>
   </si>
   <si>
     <t>9153</t>
   </si>
   <si>
-    <t>21520-21539</t>
+    <t>121521-121540</t>
   </si>
   <si>
     <t>9161</t>
   </si>
   <si>
-    <t>22040-22059</t>
+    <t>122041-122060</t>
   </si>
   <si>
     <t>9004</t>
@@ -401,43 +401,43 @@
     <t>1006</t>
   </si>
   <si>
-    <t>9280-9299</t>
+    <t>109281-109300</t>
   </si>
   <si>
     <t>9017</t>
   </si>
   <si>
-    <t>11560-11579</t>
+    <t>111561-111580</t>
   </si>
   <si>
     <t>9050</t>
   </si>
   <si>
-    <t>13100-13119</t>
+    <t>113101-113120</t>
   </si>
   <si>
     <t>9061</t>
   </si>
   <si>
-    <t>13980-13999</t>
+    <t>113981-114000</t>
   </si>
   <si>
     <t>9065</t>
   </si>
   <si>
-    <t>14860-14879</t>
+    <t>114861-114880</t>
   </si>
   <si>
     <t>9087</t>
   </si>
   <si>
-    <t>15740-15759</t>
+    <t>115741-115760</t>
   </si>
   <si>
     <t>9162</t>
   </si>
   <si>
-    <t>22300-22319</t>
+    <t>122301-122320</t>
   </si>
   <si>
     <t>Nodal Extra</t>
@@ -449,34 +449,34 @@
     <t>1007</t>
   </si>
   <si>
-    <t>22980-23079</t>
+    <t>122981-123080</t>
   </si>
   <si>
     <t>1008</t>
   </si>
   <si>
-    <t>960-1059</t>
-  </si>
-  <si>
-    <t>2780-2879</t>
-  </si>
-  <si>
-    <t>4480-4579</t>
+    <t>100961-101060</t>
+  </si>
+  <si>
+    <t>102781-102880</t>
+  </si>
+  <si>
+    <t>104481-104580</t>
   </si>
   <si>
     <t>4 to 8</t>
   </si>
   <si>
-    <t>6600-6699</t>
-  </si>
-  <si>
-    <t>16840-16939</t>
+    <t>106601-106700</t>
+  </si>
+  <si>
+    <t>116841-116940</t>
   </si>
   <si>
     <t>2 to 3</t>
   </si>
   <si>
-    <t>17600-17639</t>
+    <t>117601-117640</t>
   </si>
   <si>
     <t>4 to 6</t>
@@ -485,49 +485,49 @@
     <t>1009</t>
   </si>
   <si>
-    <t>17640-17699</t>
-  </si>
-  <si>
-    <t>17740-17839</t>
-  </si>
-  <si>
-    <t>18500-18599</t>
-  </si>
-  <si>
-    <t>20020-20119</t>
-  </si>
-  <si>
-    <t>21400-21499</t>
-  </si>
-  <si>
-    <t>21680-21779</t>
+    <t>117641-117700</t>
+  </si>
+  <si>
+    <t>117741-117840</t>
+  </si>
+  <si>
+    <t>118501-118600</t>
+  </si>
+  <si>
+    <t>120021-120120</t>
+  </si>
+  <si>
+    <t>121401-121500</t>
+  </si>
+  <si>
+    <t>121681-121780</t>
   </si>
   <si>
     <t>1010</t>
   </si>
   <si>
-    <t>20-119</t>
-  </si>
-  <si>
-    <t>1580-1679</t>
-  </si>
-  <si>
-    <t>3160-3259</t>
-  </si>
-  <si>
-    <t>4200-4299</t>
+    <t>100021-100120</t>
+  </si>
+  <si>
+    <t>101581-101680</t>
+  </si>
+  <si>
+    <t>103161-103260</t>
+  </si>
+  <si>
+    <t>104201-104300</t>
   </si>
   <si>
     <t>3 to 7</t>
   </si>
   <si>
-    <t>7980-8079</t>
+    <t>107981-108080</t>
   </si>
   <si>
     <t>2 to 2</t>
   </si>
   <si>
-    <t>8620-8639</t>
+    <t>108621-108640</t>
   </si>
   <si>
     <t>3 to 6</t>
@@ -536,127 +536,127 @@
     <t>1011</t>
   </si>
   <si>
-    <t>8640-8719</t>
-  </si>
-  <si>
-    <t>9040-9139</t>
-  </si>
-  <si>
-    <t>9680-9779</t>
-  </si>
-  <si>
-    <t>10820-10919</t>
-  </si>
-  <si>
-    <t>13500-13599</t>
+    <t>108641-108720</t>
+  </si>
+  <si>
+    <t>109041-109140</t>
+  </si>
+  <si>
+    <t>109681-109780</t>
+  </si>
+  <si>
+    <t>110821-110920</t>
+  </si>
+  <si>
+    <t>113501-113600</t>
   </si>
   <si>
     <t>1012</t>
   </si>
   <si>
-    <t>14620-14719</t>
-  </si>
-  <si>
-    <t>15140-15239</t>
+    <t>114621-114720</t>
+  </si>
+  <si>
+    <t>115141-115240</t>
   </si>
   <si>
     <t>1013</t>
   </si>
   <si>
-    <t>560-659</t>
-  </si>
-  <si>
-    <t>2640-2739</t>
-  </si>
-  <si>
-    <t>4340-4439</t>
-  </si>
-  <si>
-    <t>5120-5219</t>
-  </si>
-  <si>
-    <t>8760-8859</t>
-  </si>
-  <si>
-    <t>11960-11979</t>
+    <t>100561-100660</t>
+  </si>
+  <si>
+    <t>102641-102740</t>
+  </si>
+  <si>
+    <t>104341-104440</t>
+  </si>
+  <si>
+    <t>105121-105220</t>
+  </si>
+  <si>
+    <t>108761-108860</t>
+  </si>
+  <si>
+    <t>111961-111980</t>
   </si>
   <si>
     <t>1014</t>
   </si>
   <si>
-    <t>11980-12059</t>
-  </si>
-  <si>
-    <t>12460-12559</t>
-  </si>
-  <si>
-    <t>12720-12819</t>
-  </si>
-  <si>
-    <t>16160-16259</t>
-  </si>
-  <si>
-    <t>22460-22559</t>
+    <t>111981-112060</t>
+  </si>
+  <si>
+    <t>112461-112560</t>
+  </si>
+  <si>
+    <t>112721-112820</t>
+  </si>
+  <si>
+    <t>116161-116260</t>
+  </si>
+  <si>
+    <t>122461-122560</t>
   </si>
   <si>
     <t>1015</t>
   </si>
   <si>
-    <t>5900-5999</t>
-  </si>
-  <si>
-    <t>7300-7399</t>
-  </si>
-  <si>
-    <t>8900-8999</t>
-  </si>
-  <si>
-    <t>17220-17319</t>
-  </si>
-  <si>
-    <t>18120-18219</t>
-  </si>
-  <si>
-    <t>19000-19099</t>
-  </si>
-  <si>
-    <t>19260-19279</t>
+    <t>105901-106000</t>
+  </si>
+  <si>
+    <t>107301-107400</t>
+  </si>
+  <si>
+    <t>108901-109000</t>
+  </si>
+  <si>
+    <t>117221-117320</t>
+  </si>
+  <si>
+    <t>118121-118220</t>
+  </si>
+  <si>
+    <t>119001-119100</t>
+  </si>
+  <si>
+    <t>119261-119280</t>
   </si>
   <si>
     <t>1016</t>
   </si>
   <si>
-    <t>19280-19359</t>
-  </si>
-  <si>
-    <t>20520-20619</t>
-  </si>
-  <si>
-    <t>21540-21639</t>
-  </si>
-  <si>
-    <t>22060-22159</t>
+    <t>119281-119360</t>
+  </si>
+  <si>
+    <t>120521-120620</t>
+  </si>
+  <si>
+    <t>121541-121640</t>
+  </si>
+  <si>
+    <t>122061-122160</t>
   </si>
   <si>
     <t>1017</t>
   </si>
   <si>
-    <t>9300-9399</t>
-  </si>
-  <si>
-    <t>11580-11679</t>
-  </si>
-  <si>
-    <t>13120-13219</t>
-  </si>
-  <si>
-    <t>14000-14099</t>
+    <t>109301-109400</t>
+  </si>
+  <si>
+    <t>111581-111680</t>
+  </si>
+  <si>
+    <t>113121-113220</t>
+  </si>
+  <si>
+    <t>114001-114100</t>
   </si>
   <si>
     <t>2 to 5</t>
   </si>
   <si>
-    <t>14880-14959</t>
+    <t>114881-114960</t>
   </si>
   <si>
     <t>6 to 6</t>
@@ -665,13 +665,13 @@
     <t>1018</t>
   </si>
   <si>
-    <t>14960-14979</t>
-  </si>
-  <si>
-    <t>15760-15859</t>
-  </si>
-  <si>
-    <t>22320-22419</t>
+    <t>114961-114980</t>
+  </si>
+  <si>
+    <t>115761-115860</t>
+  </si>
+  <si>
+    <t>122321-122420</t>
   </si>
   <si>
     <t>2202</t>
@@ -683,7 +683,7 @@
     <t>1019</t>
   </si>
   <si>
-    <t>23080-23099</t>
+    <t>123081-123100</t>
   </si>
   <si>
     <t>5008</t>
@@ -692,46 +692,46 @@
     <t>1020</t>
   </si>
   <si>
-    <t>680-699</t>
-  </si>
-  <si>
-    <t>1060-1079</t>
+    <t>100681-100700</t>
+  </si>
+  <si>
+    <t>101061-101080</t>
   </si>
   <si>
     <t>5090</t>
   </si>
   <si>
-    <t>1700-1719</t>
-  </si>
-  <si>
-    <t>2880-2899</t>
-  </si>
-  <si>
-    <t>4580-4599</t>
+    <t>101701-101720</t>
+  </si>
+  <si>
+    <t>102881-102900</t>
+  </si>
+  <si>
+    <t>104581-104600</t>
   </si>
   <si>
     <t>9 to 10</t>
   </si>
   <si>
-    <t>6700-6739</t>
+    <t>106701-106740</t>
   </si>
   <si>
     <t>9115</t>
   </si>
   <si>
-    <t>16540-16559</t>
-  </si>
-  <si>
-    <t>16940-16959</t>
-  </si>
-  <si>
-    <t>17840-17859</t>
-  </si>
-  <si>
-    <t>18600-18619</t>
-  </si>
-  <si>
-    <t>21780-21799</t>
+    <t>116541-116560</t>
+  </si>
+  <si>
+    <t>116941-116960</t>
+  </si>
+  <si>
+    <t>117841-117860</t>
+  </si>
+  <si>
+    <t>118601-118620</t>
+  </si>
+  <si>
+    <t>121781-121800</t>
   </si>
   <si>
     <t>5091</t>
@@ -740,40 +740,40 @@
     <t>1021</t>
   </si>
   <si>
-    <t>2080-2119</t>
+    <t>102081-102120</t>
   </si>
   <si>
     <t>5093</t>
   </si>
   <si>
-    <t>2480-2499</t>
-  </si>
-  <si>
-    <t>3260-3279</t>
+    <t>102481-102500</t>
+  </si>
+  <si>
+    <t>103261-103280</t>
   </si>
   <si>
     <t>8 to 8</t>
   </si>
   <si>
-    <t>8080-8099</t>
-  </si>
-  <si>
-    <t>9140-9159</t>
-  </si>
-  <si>
-    <t>9780-9799</t>
-  </si>
-  <si>
-    <t>10920-10939</t>
-  </si>
-  <si>
-    <t>13600-13619</t>
-  </si>
-  <si>
-    <t>14720-14739</t>
-  </si>
-  <si>
-    <t>15240-15259</t>
+    <t>108081-108100</t>
+  </si>
+  <si>
+    <t>109141-109160</t>
+  </si>
+  <si>
+    <t>109781-109800</t>
+  </si>
+  <si>
+    <t>110921-110940</t>
+  </si>
+  <si>
+    <t>113601-113620</t>
+  </si>
+  <si>
+    <t>114721-114740</t>
+  </si>
+  <si>
+    <t>115241-115260</t>
   </si>
   <si>
     <t>5140</t>
@@ -782,40 +782,40 @@
     <t>1022</t>
   </si>
   <si>
-    <t>3800-3819</t>
+    <t>103801-103820</t>
   </si>
   <si>
     <t>8 to 11</t>
   </si>
   <si>
-    <t>5220-5299</t>
-  </si>
-  <si>
-    <t>12060-12079</t>
+    <t>105221-105300</t>
+  </si>
+  <si>
+    <t>112061-112080</t>
   </si>
   <si>
     <t>9034</t>
   </si>
   <si>
-    <t>12960-12979</t>
-  </si>
-  <si>
-    <t>16260-16279</t>
+    <t>112961-112980</t>
+  </si>
+  <si>
+    <t>116261-116280</t>
   </si>
   <si>
     <t>9108</t>
   </si>
   <si>
-    <t>16400-16419</t>
-  </si>
-  <si>
-    <t>22560-22579</t>
+    <t>116401-116420</t>
+  </si>
+  <si>
+    <t>122561-122580</t>
   </si>
   <si>
     <t>9172</t>
   </si>
   <si>
-    <t>22700-22719</t>
+    <t>122701-122720</t>
   </si>
   <si>
     <t>7 to 8</t>
@@ -824,55 +824,55 @@
     <t>1023</t>
   </si>
   <si>
-    <t>6000-6039</t>
-  </si>
-  <si>
-    <t>7400-7439</t>
+    <t>106001-106040</t>
+  </si>
+  <si>
+    <t>107401-107440</t>
   </si>
   <si>
     <t>9117</t>
   </si>
   <si>
-    <t>16680-16699</t>
-  </si>
-  <si>
-    <t>17320-17339</t>
-  </si>
-  <si>
-    <t>19360-19379</t>
-  </si>
-  <si>
-    <t>20620-20639</t>
+    <t>116681-116700</t>
+  </si>
+  <si>
+    <t>117321-117340</t>
+  </si>
+  <si>
+    <t>119361-119380</t>
+  </si>
+  <si>
+    <t>120621-120640</t>
   </si>
   <si>
     <t>9148</t>
   </si>
   <si>
-    <t>20880-20899</t>
+    <t>120881-120900</t>
   </si>
   <si>
     <t>1024</t>
   </si>
   <si>
-    <t>9400-9419</t>
+    <t>109401-109420</t>
   </si>
   <si>
     <t>9010</t>
   </si>
   <si>
-    <t>10280-10299</t>
-  </si>
-  <si>
-    <t>13220-13239</t>
-  </si>
-  <si>
-    <t>14100-14119</t>
-  </si>
-  <si>
-    <t>14980-14999</t>
-  </si>
-  <si>
-    <t>15860-15879</t>
+    <t>110281-110300</t>
+  </si>
+  <si>
+    <t>113221-113240</t>
+  </si>
+  <si>
+    <t>114101-114120</t>
+  </si>
+  <si>
+    <t>114981-115000</t>
+  </si>
+  <si>
+    <t>115861-115880</t>
   </si>
   <si>
     <t>8 to 12</t>
@@ -881,31 +881,31 @@
     <t>1025</t>
   </si>
   <si>
-    <t>23100-23199</t>
+    <t>123101-123200</t>
   </si>
   <si>
     <t>1026</t>
   </si>
   <si>
-    <t>700-799</t>
-  </si>
-  <si>
-    <t>1080-1179</t>
-  </si>
-  <si>
-    <t>1720-1819</t>
-  </si>
-  <si>
-    <t>2900-2999</t>
-  </si>
-  <si>
-    <t>4600-4699</t>
+    <t>100701-100800</t>
+  </si>
+  <si>
+    <t>101081-101180</t>
+  </si>
+  <si>
+    <t>101721-101820</t>
+  </si>
+  <si>
+    <t>102901-103000</t>
+  </si>
+  <si>
+    <t>104601-104700</t>
   </si>
   <si>
     <t>11 to 11</t>
   </si>
   <si>
-    <t>6740-6759</t>
+    <t>106741-106760</t>
   </si>
   <si>
     <t>12 to 15</t>
@@ -914,46 +914,46 @@
     <t>1027</t>
   </si>
   <si>
-    <t>6760-6839</t>
-  </si>
-  <si>
-    <t>16560-16659</t>
-  </si>
-  <si>
-    <t>16960-17059</t>
-  </si>
-  <si>
-    <t>17860-17959</t>
-  </si>
-  <si>
-    <t>18620-18719</t>
-  </si>
-  <si>
-    <t>21800-21899</t>
+    <t>106761-106840</t>
+  </si>
+  <si>
+    <t>116561-116660</t>
+  </si>
+  <si>
+    <t>116961-117060</t>
+  </si>
+  <si>
+    <t>117861-117960</t>
+  </si>
+  <si>
+    <t>118621-118720</t>
+  </si>
+  <si>
+    <t>121801-121900</t>
   </si>
   <si>
     <t>1028</t>
   </si>
   <si>
-    <t>2120-2219</t>
-  </si>
-  <si>
-    <t>2500-2599</t>
-  </si>
-  <si>
-    <t>3280-3379</t>
+    <t>102121-102220</t>
+  </si>
+  <si>
+    <t>102501-102600</t>
+  </si>
+  <si>
+    <t>103281-103380</t>
   </si>
   <si>
     <t>9 to 13</t>
   </si>
   <si>
-    <t>8100-8199</t>
-  </si>
-  <si>
-    <t>9160-9259</t>
-  </si>
-  <si>
-    <t>9800-9819</t>
+    <t>108101-108200</t>
+  </si>
+  <si>
+    <t>109161-109260</t>
+  </si>
+  <si>
+    <t>109801-109820</t>
   </si>
   <si>
     <t>9 to 12</t>
@@ -962,103 +962,103 @@
     <t>1029</t>
   </si>
   <si>
-    <t>9820-9899</t>
-  </si>
-  <si>
-    <t>10940-11039</t>
-  </si>
-  <si>
-    <t>13620-13719</t>
-  </si>
-  <si>
-    <t>14740-14839</t>
-  </si>
-  <si>
-    <t>15260-15359</t>
+    <t>109821-109900</t>
+  </si>
+  <si>
+    <t>110941-111040</t>
+  </si>
+  <si>
+    <t>113621-113720</t>
+  </si>
+  <si>
+    <t>114741-114840</t>
+  </si>
+  <si>
+    <t>115261-115360</t>
   </si>
   <si>
     <t>1030</t>
   </si>
   <si>
-    <t>3820-3919</t>
+    <t>103821-103920</t>
   </si>
   <si>
     <t>12 to 16</t>
   </si>
   <si>
-    <t>5300-5399</t>
-  </si>
-  <si>
-    <t>12080-12179</t>
-  </si>
-  <si>
-    <t>12980-13079</t>
-  </si>
-  <si>
-    <t>16280-16379</t>
-  </si>
-  <si>
-    <t>16420-16519</t>
-  </si>
-  <si>
-    <t>22580-22599</t>
+    <t>105301-105400</t>
+  </si>
+  <si>
+    <t>112081-112180</t>
+  </si>
+  <si>
+    <t>112981-113080</t>
+  </si>
+  <si>
+    <t>116281-116380</t>
+  </si>
+  <si>
+    <t>116421-116520</t>
+  </si>
+  <si>
+    <t>122581-122600</t>
   </si>
   <si>
     <t>1031</t>
   </si>
   <si>
-    <t>22600-22679</t>
-  </si>
-  <si>
-    <t>22720-22819</t>
+    <t>122601-122680</t>
+  </si>
+  <si>
+    <t>122721-122820</t>
   </si>
   <si>
     <t>1032</t>
   </si>
   <si>
-    <t>6040-6139</t>
-  </si>
-  <si>
-    <t>7440-7539</t>
-  </si>
-  <si>
-    <t>16700-16799</t>
-  </si>
-  <si>
-    <t>17340-17439</t>
-  </si>
-  <si>
-    <t>19380-19479</t>
-  </si>
-  <si>
-    <t>20640-20739</t>
-  </si>
-  <si>
-    <t>20900-20919</t>
+    <t>106041-106140</t>
+  </si>
+  <si>
+    <t>107441-107540</t>
+  </si>
+  <si>
+    <t>116701-116800</t>
+  </si>
+  <si>
+    <t>117341-117440</t>
+  </si>
+  <si>
+    <t>119381-119480</t>
+  </si>
+  <si>
+    <t>120641-120740</t>
+  </si>
+  <si>
+    <t>120901-120920</t>
   </si>
   <si>
     <t>1033</t>
   </si>
   <si>
-    <t>20920-20999</t>
+    <t>120921-121000</t>
   </si>
   <si>
     <t>1034</t>
   </si>
   <si>
-    <t>9420-9519</t>
-  </si>
-  <si>
-    <t>10300-10399</t>
-  </si>
-  <si>
-    <t>13240-13339</t>
-  </si>
-  <si>
-    <t>14120-14219</t>
-  </si>
-  <si>
-    <t>15000-15079</t>
+    <t>109421-109520</t>
+  </si>
+  <si>
+    <t>110301-110400</t>
+  </si>
+  <si>
+    <t>113241-113340</t>
+  </si>
+  <si>
+    <t>114121-114220</t>
+  </si>
+  <si>
+    <t>115001-115080</t>
   </si>
   <si>
     <t>12 to 12</t>
@@ -1067,10 +1067,10 @@
     <t>1035</t>
   </si>
   <si>
-    <t>15080-15099</t>
-  </si>
-  <si>
-    <t>15880-15979</t>
+    <t>115081-115100</t>
+  </si>
+  <si>
+    <t>115881-115980</t>
   </si>
   <si>
     <t>2208</t>
@@ -1082,70 +1082,70 @@
     <t>1036</t>
   </si>
   <si>
-    <t>23200-23219</t>
+    <t>123201-123220</t>
   </si>
   <si>
     <t>1037</t>
   </si>
   <si>
-    <t>800-819</t>
-  </si>
-  <si>
-    <t>1180-1199</t>
-  </si>
-  <si>
-    <t>3000-3019</t>
-  </si>
-  <si>
-    <t>4700-4719</t>
+    <t>100801-100820</t>
+  </si>
+  <si>
+    <t>101181-101200</t>
+  </si>
+  <si>
+    <t>103001-103020</t>
+  </si>
+  <si>
+    <t>104701-104720</t>
   </si>
   <si>
     <t>16 to 19</t>
   </si>
   <si>
-    <t>6840-6919</t>
-  </si>
-  <si>
-    <t>17060-17079</t>
-  </si>
-  <si>
-    <t>17960-17979</t>
-  </si>
-  <si>
-    <t>18720-18739</t>
-  </si>
-  <si>
-    <t>20120-20139</t>
-  </si>
-  <si>
-    <t>21900-21919</t>
+    <t>106841-106920</t>
+  </si>
+  <si>
+    <t>117061-117080</t>
+  </si>
+  <si>
+    <t>117961-117980</t>
+  </si>
+  <si>
+    <t>118721-118740</t>
+  </si>
+  <si>
+    <t>120121-120140</t>
+  </si>
+  <si>
+    <t>121901-121920</t>
   </si>
   <si>
     <t>1038</t>
   </si>
   <si>
-    <t>120-139</t>
-  </si>
-  <si>
-    <t>3380-3399</t>
+    <t>100121-100140</t>
+  </si>
+  <si>
+    <t>103381-103400</t>
   </si>
   <si>
     <t>14 to 14</t>
   </si>
   <si>
-    <t>8200-8219</t>
-  </si>
-  <si>
-    <t>9900-9919</t>
-  </si>
-  <si>
-    <t>11040-11059</t>
-  </si>
-  <si>
-    <t>13720-13739</t>
-  </si>
-  <si>
-    <t>15360-15379</t>
+    <t>108201-108220</t>
+  </si>
+  <si>
+    <t>109901-109920</t>
+  </si>
+  <si>
+    <t>111041-111060</t>
+  </si>
+  <si>
+    <t>113721-113740</t>
+  </si>
+  <si>
+    <t>115361-115380</t>
   </si>
   <si>
     <t>1254</t>
@@ -1154,28 +1154,28 @@
     <t>1039</t>
   </si>
   <si>
-    <t>260-279</t>
+    <t>100261-100280</t>
   </si>
   <si>
     <t>5122</t>
   </si>
   <si>
-    <t>3520-3539</t>
+    <t>103521-103540</t>
   </si>
   <si>
     <t>17 to 21</t>
   </si>
   <si>
-    <t>5400-5499</t>
-  </si>
-  <si>
-    <t>12180-12199</t>
-  </si>
-  <si>
-    <t>12560-12579</t>
-  </si>
-  <si>
-    <t>22820-22839</t>
+    <t>105401-105500</t>
+  </si>
+  <si>
+    <t>112181-112200</t>
+  </si>
+  <si>
+    <t>112561-112580</t>
+  </si>
+  <si>
+    <t>122821-122840</t>
   </si>
   <si>
     <t>14 to 15</t>
@@ -1184,31 +1184,31 @@
     <t>1040</t>
   </si>
   <si>
-    <t>6140-6179</t>
-  </si>
-  <si>
-    <t>7540-7579</t>
-  </si>
-  <si>
-    <t>17440-17459</t>
-  </si>
-  <si>
-    <t>18220-18239</t>
-  </si>
-  <si>
-    <t>19100-19119</t>
-  </si>
-  <si>
-    <t>19480-19499</t>
-  </si>
-  <si>
-    <t>20740-20759</t>
-  </si>
-  <si>
-    <t>21000-21019</t>
-  </si>
-  <si>
-    <t>22160-22179</t>
+    <t>106141-106180</t>
+  </si>
+  <si>
+    <t>107541-107580</t>
+  </si>
+  <si>
+    <t>117441-117460</t>
+  </si>
+  <si>
+    <t>118221-118240</t>
+  </si>
+  <si>
+    <t>119101-119120</t>
+  </si>
+  <si>
+    <t>119481-119500</t>
+  </si>
+  <si>
+    <t>120741-120760</t>
+  </si>
+  <si>
+    <t>121001-121020</t>
+  </si>
+  <si>
+    <t>122161-122180</t>
   </si>
   <si>
     <t>1255</t>
@@ -1217,22 +1217,22 @@
     <t>1041</t>
   </si>
   <si>
-    <t>400-419</t>
-  </si>
-  <si>
-    <t>9520-9539</t>
-  </si>
-  <si>
-    <t>10400-10419</t>
-  </si>
-  <si>
-    <t>11680-11699</t>
-  </si>
-  <si>
-    <t>13340-13359</t>
-  </si>
-  <si>
-    <t>14220-14239</t>
+    <t>100401-100420</t>
+  </si>
+  <si>
+    <t>109521-109540</t>
+  </si>
+  <si>
+    <t>110401-110420</t>
+  </si>
+  <si>
+    <t>111681-111700</t>
+  </si>
+  <si>
+    <t>113341-113360</t>
+  </si>
+  <si>
+    <t>114221-114240</t>
   </si>
   <si>
     <t>14 to 18</t>
@@ -1241,31 +1241,31 @@
     <t>1042</t>
   </si>
   <si>
-    <t>23220-23319</t>
+    <t>123221-123320</t>
   </si>
   <si>
     <t>1043</t>
   </si>
   <si>
-    <t>820-919</t>
-  </si>
-  <si>
-    <t>1200-1299</t>
-  </si>
-  <si>
-    <t>3020-3119</t>
-  </si>
-  <si>
-    <t>4720-4819</t>
+    <t>100821-100920</t>
+  </si>
+  <si>
+    <t>101201-101300</t>
+  </si>
+  <si>
+    <t>103021-103120</t>
+  </si>
+  <si>
+    <t>104721-104820</t>
   </si>
   <si>
     <t>20 to 24</t>
   </si>
   <si>
-    <t>6920-7019</t>
-  </si>
-  <si>
-    <t>17080-17099</t>
+    <t>106921-107020</t>
+  </si>
+  <si>
+    <t>117081-117100</t>
   </si>
   <si>
     <t>15 to 18</t>
@@ -1274,43 +1274,43 @@
     <t>1044</t>
   </si>
   <si>
-    <t>17100-17179</t>
-  </si>
-  <si>
-    <t>17980-18079</t>
-  </si>
-  <si>
-    <t>18740-18839</t>
-  </si>
-  <si>
-    <t>20140-20239</t>
-  </si>
-  <si>
-    <t>21920-22019</t>
+    <t>117101-117180</t>
+  </si>
+  <si>
+    <t>117981-118080</t>
+  </si>
+  <si>
+    <t>118741-118840</t>
+  </si>
+  <si>
+    <t>120141-120240</t>
+  </si>
+  <si>
+    <t>121921-122020</t>
   </si>
   <si>
     <t>1045</t>
   </si>
   <si>
-    <t>140-239</t>
-  </si>
-  <si>
-    <t>3400-3499</t>
+    <t>100141-100240</t>
+  </si>
+  <si>
+    <t>103401-103500</t>
   </si>
   <si>
     <t>15 to 19</t>
   </si>
   <si>
-    <t>8220-8319</t>
-  </si>
-  <si>
-    <t>9920-10019</t>
+    <t>108221-108320</t>
+  </si>
+  <si>
+    <t>109921-110020</t>
   </si>
   <si>
     <t>14 to 17</t>
   </si>
   <si>
-    <t>11060-11139</t>
+    <t>111061-111140</t>
   </si>
   <si>
     <t>18 to 18</t>
@@ -1319,43 +1319,43 @@
     <t>1046</t>
   </si>
   <si>
-    <t>11140-11159</t>
-  </si>
-  <si>
-    <t>13740-13839</t>
-  </si>
-  <si>
-    <t>15380-15479</t>
+    <t>111141-111160</t>
+  </si>
+  <si>
+    <t>113741-113840</t>
+  </si>
+  <si>
+    <t>115381-115480</t>
   </si>
   <si>
     <t>1047</t>
   </si>
   <si>
-    <t>280-379</t>
-  </si>
-  <si>
-    <t>3540-3639</t>
+    <t>100281-100380</t>
+  </si>
+  <si>
+    <t>103541-103640</t>
   </si>
   <si>
     <t>22 to 26</t>
   </si>
   <si>
-    <t>5500-5599</t>
-  </si>
-  <si>
-    <t>12200-12299</t>
-  </si>
-  <si>
-    <t>12580-12679</t>
-  </si>
-  <si>
-    <t>22840-22919</t>
+    <t>105501-105600</t>
+  </si>
+  <si>
+    <t>112201-112300</t>
+  </si>
+  <si>
+    <t>112581-112680</t>
+  </si>
+  <si>
+    <t>122841-122920</t>
   </si>
   <si>
     <t>1048</t>
   </si>
   <si>
-    <t>22920-22939</t>
+    <t>122921-122940</t>
   </si>
   <si>
     <t>16 to 20</t>
@@ -1364,64 +1364,64 @@
     <t>1049</t>
   </si>
   <si>
-    <t>6180-6279</t>
-  </si>
-  <si>
-    <t>7580-7679</t>
-  </si>
-  <si>
-    <t>17460-17559</t>
-  </si>
-  <si>
-    <t>18240-18339</t>
-  </si>
-  <si>
-    <t>19120-19219</t>
-  </si>
-  <si>
-    <t>19500-19599</t>
-  </si>
-  <si>
-    <t>20760-20779</t>
+    <t>106181-106280</t>
+  </si>
+  <si>
+    <t>107581-107680</t>
+  </si>
+  <si>
+    <t>117461-117560</t>
+  </si>
+  <si>
+    <t>118241-118340</t>
+  </si>
+  <si>
+    <t>119121-119220</t>
+  </si>
+  <si>
+    <t>119501-119600</t>
+  </si>
+  <si>
+    <t>120761-120780</t>
   </si>
   <si>
     <t>1050</t>
   </si>
   <si>
-    <t>20780-20859</t>
-  </si>
-  <si>
-    <t>21020-21119</t>
-  </si>
-  <si>
-    <t>22180-22279</t>
+    <t>120781-120860</t>
+  </si>
+  <si>
+    <t>121021-121120</t>
+  </si>
+  <si>
+    <t>122181-122280</t>
   </si>
   <si>
     <t>1051</t>
   </si>
   <si>
-    <t>420-519</t>
-  </si>
-  <si>
-    <t>9540-9639</t>
-  </si>
-  <si>
-    <t>10420-10519</t>
-  </si>
-  <si>
-    <t>11700-11799</t>
-  </si>
-  <si>
-    <t>13360-13439</t>
+    <t>100421-100520</t>
+  </si>
+  <si>
+    <t>109541-109640</t>
+  </si>
+  <si>
+    <t>110421-110520</t>
+  </si>
+  <si>
+    <t>111701-111800</t>
+  </si>
+  <si>
+    <t>113361-113440</t>
   </si>
   <si>
     <t>1052</t>
   </si>
   <si>
-    <t>13440-13459</t>
-  </si>
-  <si>
-    <t>14240-14339</t>
+    <t>113441-113460</t>
+  </si>
+  <si>
+    <t>114241-114340</t>
   </si>
   <si>
     <t>2205</t>
@@ -1433,43 +1433,43 @@
     <t>1053</t>
   </si>
   <si>
-    <t>1300-1319</t>
-  </si>
-  <si>
-    <t>1820-1839</t>
-  </si>
-  <si>
-    <t>4820-4839</t>
+    <t>101301-101320</t>
+  </si>
+  <si>
+    <t>101821-101840</t>
+  </si>
+  <si>
+    <t>104821-104840</t>
   </si>
   <si>
     <t>25 to 25</t>
   </si>
   <si>
-    <t>7020-7039</t>
-  </si>
-  <si>
-    <t>20240-20259</t>
+    <t>107021-107040</t>
+  </si>
+  <si>
+    <t>120241-120260</t>
   </si>
   <si>
     <t>1054</t>
   </si>
   <si>
-    <t>2220-2239</t>
+    <t>102221-102240</t>
   </si>
   <si>
     <t>20 to 21</t>
   </si>
   <si>
-    <t>8320-8359</t>
-  </si>
-  <si>
-    <t>10020-10039</t>
-  </si>
-  <si>
-    <t>11160-11179</t>
-  </si>
-  <si>
-    <t>15480-15499</t>
+    <t>108321-108360</t>
+  </si>
+  <si>
+    <t>110021-110040</t>
+  </si>
+  <si>
+    <t>111161-111180</t>
+  </si>
+  <si>
+    <t>115481-115500</t>
   </si>
   <si>
     <t>5138</t>
@@ -1478,19 +1478,19 @@
     <t>1055</t>
   </si>
   <si>
-    <t>3660-3679</t>
-  </si>
-  <si>
-    <t>3920-3939</t>
+    <t>103661-103680</t>
+  </si>
+  <si>
+    <t>103921-103940</t>
   </si>
   <si>
     <t>27 to 28</t>
   </si>
   <si>
-    <t>5600-5639</t>
-  </si>
-  <si>
-    <t>12300-12319</t>
+    <t>105601-105640</t>
+  </si>
+  <si>
+    <t>112301-112320</t>
   </si>
   <si>
     <t>21 to 21</t>
@@ -1499,91 +1499,91 @@
     <t>1056</t>
   </si>
   <si>
-    <t>6280-6299</t>
-  </si>
-  <si>
-    <t>7680-7699</t>
-  </si>
-  <si>
-    <t>18340-18359</t>
-  </si>
-  <si>
-    <t>19600-19619</t>
+    <t>106281-106300</t>
+  </si>
+  <si>
+    <t>107681-107700</t>
+  </si>
+  <si>
+    <t>118341-118360</t>
+  </si>
+  <si>
+    <t>119601-119620</t>
   </si>
   <si>
     <t>9143</t>
   </si>
   <si>
-    <t>19860-19879</t>
-  </si>
-  <si>
-    <t>21120-21139</t>
+    <t>119861-119880</t>
+  </si>
+  <si>
+    <t>121121-121140</t>
   </si>
   <si>
     <t>1057</t>
   </si>
   <si>
-    <t>10520-10539</t>
+    <t>110521-110540</t>
   </si>
   <si>
     <t>9012</t>
   </si>
   <si>
-    <t>10660-10679</t>
+    <t>110661-110680</t>
   </si>
   <si>
     <t>9016</t>
   </si>
   <si>
-    <t>11420-11439</t>
-  </si>
-  <si>
-    <t>11800-11819</t>
-  </si>
-  <si>
-    <t>14340-14359</t>
+    <t>111421-111440</t>
+  </si>
+  <si>
+    <t>111801-111820</t>
+  </si>
+  <si>
+    <t>114341-114360</t>
   </si>
   <si>
     <t>1058</t>
   </si>
   <si>
-    <t>1320-1419</t>
-  </si>
-  <si>
-    <t>1840-1939</t>
-  </si>
-  <si>
-    <t>4840-4939</t>
+    <t>101321-101420</t>
+  </si>
+  <si>
+    <t>101841-101940</t>
+  </si>
+  <si>
+    <t>104841-104940</t>
   </si>
   <si>
     <t>26 to 30</t>
   </si>
   <si>
-    <t>7040-7139</t>
-  </si>
-  <si>
-    <t>20260-20359</t>
+    <t>107041-107140</t>
+  </si>
+  <si>
+    <t>120261-120360</t>
   </si>
   <si>
     <t>1059</t>
   </si>
   <si>
-    <t>2240-2339</t>
-  </si>
-  <si>
-    <t>8360-8459</t>
-  </si>
-  <si>
-    <t>10040-10139</t>
-  </si>
-  <si>
-    <t>11180-11279</t>
+    <t>102241-102340</t>
+  </si>
+  <si>
+    <t>108361-108460</t>
+  </si>
+  <si>
+    <t>110041-110140</t>
+  </si>
+  <si>
+    <t>111181-111280</t>
   </si>
   <si>
     <t>20 to 23</t>
   </si>
   <si>
-    <t>15500-15579</t>
+    <t>115501-115580</t>
   </si>
   <si>
     <t>24 to 24</t>
@@ -1592,64 +1592,64 @@
     <t>1060</t>
   </si>
   <si>
-    <t>15580-15599</t>
+    <t>115581-115600</t>
   </si>
   <si>
     <t>1061</t>
   </si>
   <si>
-    <t>3680-3779</t>
-  </si>
-  <si>
-    <t>3940-4039</t>
+    <t>103681-103780</t>
+  </si>
+  <si>
+    <t>103941-104040</t>
   </si>
   <si>
     <t>29 to 33</t>
   </si>
   <si>
-    <t>5640-5739</t>
-  </si>
-  <si>
-    <t>12320-12419</t>
+    <t>105641-105740</t>
+  </si>
+  <si>
+    <t>112321-112420</t>
   </si>
   <si>
     <t>1062</t>
   </si>
   <si>
-    <t>6300-6399</t>
-  </si>
-  <si>
-    <t>7700-7799</t>
-  </si>
-  <si>
-    <t>18360-18459</t>
-  </si>
-  <si>
-    <t>19620-19719</t>
-  </si>
-  <si>
-    <t>19880-19979</t>
-  </si>
-  <si>
-    <t>21140-21239</t>
+    <t>106301-106400</t>
+  </si>
+  <si>
+    <t>107701-107800</t>
+  </si>
+  <si>
+    <t>118361-118460</t>
+  </si>
+  <si>
+    <t>119621-119720</t>
+  </si>
+  <si>
+    <t>119881-119980</t>
+  </si>
+  <si>
+    <t>121141-121240</t>
   </si>
   <si>
     <t>1063</t>
   </si>
   <si>
-    <t>10540-10639</t>
-  </si>
-  <si>
-    <t>10680-10779</t>
-  </si>
-  <si>
-    <t>11440-11539</t>
-  </si>
-  <si>
-    <t>11820-11919</t>
-  </si>
-  <si>
-    <t>14360-14459</t>
+    <t>110541-110640</t>
+  </si>
+  <si>
+    <t>110681-110780</t>
+  </si>
+  <si>
+    <t>111441-111540</t>
+  </si>
+  <si>
+    <t>111821-111920</t>
+  </si>
+  <si>
+    <t>114361-114460</t>
   </si>
   <si>
     <t>2212</t>
@@ -1658,184 +1658,184 @@
     <t>1064</t>
   </si>
   <si>
-    <t>1420-1439</t>
-  </si>
-  <si>
-    <t>1940-1959</t>
-  </si>
-  <si>
-    <t>4940-4959</t>
+    <t>101421-101440</t>
+  </si>
+  <si>
+    <t>101941-101960</t>
+  </si>
+  <si>
+    <t>104941-104960</t>
   </si>
   <si>
     <t>31 to 31</t>
   </si>
   <si>
-    <t>7140-7159</t>
-  </si>
-  <si>
-    <t>18840-18859</t>
-  </si>
-  <si>
-    <t>20360-20379</t>
+    <t>107141-107160</t>
+  </si>
+  <si>
+    <t>118841-118860</t>
+  </si>
+  <si>
+    <t>120361-120380</t>
   </si>
   <si>
     <t>1065</t>
   </si>
   <si>
-    <t>2340-2359</t>
+    <t>102341-102360</t>
   </si>
   <si>
     <t>27 to 27</t>
   </si>
   <si>
-    <t>8460-8479</t>
-  </si>
-  <si>
-    <t>10140-10159</t>
-  </si>
-  <si>
-    <t>11280-11299</t>
-  </si>
-  <si>
-    <t>13840-13859</t>
-  </si>
-  <si>
-    <t>15600-15619</t>
+    <t>108461-108480</t>
+  </si>
+  <si>
+    <t>110141-110160</t>
+  </si>
+  <si>
+    <t>111281-111300</t>
+  </si>
+  <si>
+    <t>113841-113860</t>
+  </si>
+  <si>
+    <t>115601-115620</t>
   </si>
   <si>
     <t>1066</t>
   </si>
   <si>
-    <t>4040-4059</t>
+    <t>104041-104060</t>
   </si>
   <si>
     <t>34 to 34</t>
   </si>
   <si>
-    <t>5740-5759</t>
-  </si>
-  <si>
-    <t>12820-12839</t>
+    <t>105741-105760</t>
+  </si>
+  <si>
+    <t>112821-112840</t>
   </si>
   <si>
     <t>1067</t>
   </si>
   <si>
-    <t>6400-6419</t>
-  </si>
-  <si>
-    <t>7800-7819</t>
-  </si>
-  <si>
-    <t>19720-19739</t>
-  </si>
-  <si>
-    <t>21240-21259</t>
+    <t>106401-106420</t>
+  </si>
+  <si>
+    <t>107801-107820</t>
+  </si>
+  <si>
+    <t>119721-119740</t>
+  </si>
+  <si>
+    <t>121241-121260</t>
   </si>
   <si>
     <t>1068</t>
   </si>
   <si>
-    <t>14460-14479</t>
+    <t>114461-114480</t>
   </si>
   <si>
     <t>9088</t>
   </si>
   <si>
-    <t>16000-16019</t>
+    <t>116001-116020</t>
   </si>
   <si>
     <t>1069</t>
   </si>
   <si>
-    <t>1440-1539</t>
-  </si>
-  <si>
-    <t>1960-2059</t>
-  </si>
-  <si>
-    <t>4960-5059</t>
+    <t>101441-101540</t>
+  </si>
+  <si>
+    <t>101961-102060</t>
+  </si>
+  <si>
+    <t>104961-105060</t>
   </si>
   <si>
     <t>32 to 36</t>
   </si>
   <si>
-    <t>7160-7259</t>
-  </si>
-  <si>
-    <t>18860-18959</t>
-  </si>
-  <si>
-    <t>20380-20479</t>
+    <t>107161-107260</t>
+  </si>
+  <si>
+    <t>118861-118960</t>
+  </si>
+  <si>
+    <t>120381-120480</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>2360-2459</t>
+    <t>102361-102460</t>
   </si>
   <si>
     <t>28 to 32</t>
   </si>
   <si>
-    <t>8480-8579</t>
-  </si>
-  <si>
-    <t>10160-10259</t>
-  </si>
-  <si>
-    <t>11300-11399</t>
-  </si>
-  <si>
-    <t>13860-13939</t>
+    <t>108481-108580</t>
+  </si>
+  <si>
+    <t>110161-110260</t>
+  </si>
+  <si>
+    <t>111301-111400</t>
+  </si>
+  <si>
+    <t>113861-113940</t>
   </si>
   <si>
     <t>1071</t>
   </si>
   <si>
-    <t>13940-13959</t>
-  </si>
-  <si>
-    <t>15620-15719</t>
+    <t>113941-113960</t>
+  </si>
+  <si>
+    <t>115621-115720</t>
   </si>
   <si>
     <t>1072</t>
   </si>
   <si>
-    <t>4060-4159</t>
+    <t>104061-104160</t>
   </si>
   <si>
     <t>35 to 39</t>
   </si>
   <si>
-    <t>5760-5859</t>
-  </si>
-  <si>
-    <t>12840-12939</t>
+    <t>105761-105860</t>
+  </si>
+  <si>
+    <t>112841-112940</t>
   </si>
   <si>
     <t>1073</t>
   </si>
   <si>
-    <t>6420-6519</t>
-  </si>
-  <si>
-    <t>7820-7919</t>
-  </si>
-  <si>
-    <t>19740-19839</t>
-  </si>
-  <si>
-    <t>21260-21359</t>
+    <t>106421-106520</t>
+  </si>
+  <si>
+    <t>107821-107920</t>
+  </si>
+  <si>
+    <t>119741-119840</t>
+  </si>
+  <si>
+    <t>121261-121360</t>
   </si>
   <si>
     <t>1074</t>
   </si>
   <si>
-    <t>14480-14579</t>
-  </si>
-  <si>
-    <t>16020-16119</t>
+    <t>114481-114580</t>
+  </si>
+  <si>
+    <t>116021-116120</t>
   </si>
   <si>
     <t>University Extra</t>
@@ -1844,97 +1844,97 @@
     <t>1075</t>
   </si>
   <si>
-    <t>23320-23339</t>
+    <t>123321-123340</t>
   </si>
   <si>
     <t>1076</t>
   </si>
   <si>
-    <t>920-939</t>
+    <t>100921-100940</t>
   </si>
   <si>
     <t>1077</t>
   </si>
   <si>
-    <t>1540-1559</t>
-  </si>
-  <si>
-    <t>2060-2079</t>
+    <t>101541-101560</t>
+  </si>
+  <si>
+    <t>102061-102080</t>
   </si>
   <si>
     <t>1078</t>
   </si>
   <si>
-    <t>3120-3139</t>
+    <t>103121-103140</t>
   </si>
   <si>
     <t>1079</t>
   </si>
   <si>
-    <t>5060-5079</t>
+    <t>105061-105080</t>
   </si>
   <si>
     <t>37 to 37</t>
   </si>
   <si>
-    <t>7260-7279</t>
+    <t>107261-107280</t>
   </si>
   <si>
     <t>1080</t>
   </si>
   <si>
-    <t>16660-16679</t>
+    <t>116661-116680</t>
   </si>
   <si>
     <t>1081</t>
   </si>
   <si>
-    <t>17180-17199</t>
+    <t>117181-117200</t>
   </si>
   <si>
     <t>1082</t>
   </si>
   <si>
-    <t>17700-17719</t>
+    <t>117701-117720</t>
   </si>
   <si>
     <t>1083</t>
   </si>
   <si>
-    <t>18080-18099</t>
+    <t>118081-118100</t>
   </si>
   <si>
     <t>1084</t>
   </si>
   <si>
-    <t>18960-18979</t>
-  </si>
-  <si>
-    <t>20480-20499</t>
+    <t>118961-118980</t>
+  </si>
+  <si>
+    <t>120481-120500</t>
   </si>
   <si>
     <t>1085</t>
   </si>
   <si>
-    <t>21500-21519</t>
+    <t>121501-121520</t>
   </si>
   <si>
     <t>1086</t>
   </si>
   <si>
-    <t>22020-22039</t>
+    <t>122021-122040</t>
   </si>
   <si>
     <t>1087</t>
   </si>
   <si>
-    <t>240-259</t>
+    <t>100241-100260</t>
   </si>
   <si>
     <t>1088</t>
   </si>
   <si>
-    <t>1680-1699</t>
+    <t>101681-101700</t>
   </si>
   <si>
     <t>20 to 20</t>
@@ -1943,25 +1943,25 @@
     <t>1089</t>
   </si>
   <si>
-    <t>2460-2479</t>
+    <t>102461-102480</t>
   </si>
   <si>
     <t>1090</t>
   </si>
   <si>
-    <t>2600-2619</t>
+    <t>102601-102620</t>
   </si>
   <si>
     <t>1091</t>
   </si>
   <si>
-    <t>3500-3519</t>
+    <t>103501-103520</t>
   </si>
   <si>
     <t>1092</t>
   </si>
   <si>
-    <t>4300-4319</t>
+    <t>104301-104320</t>
   </si>
   <si>
     <t>33 to 33</t>
@@ -1970,82 +1970,82 @@
     <t>1093</t>
   </si>
   <si>
-    <t>8580-8599</t>
+    <t>108581-108600</t>
   </si>
   <si>
     <t>1094</t>
   </si>
   <si>
-    <t>8720-8739</t>
+    <t>108721-108740</t>
   </si>
   <si>
     <t>1095</t>
   </si>
   <si>
-    <t>9260-9279</t>
+    <t>109261-109280</t>
   </si>
   <si>
     <t>1096</t>
   </si>
   <si>
-    <t>10260-10279</t>
-  </si>
-  <si>
-    <t>11400-11419</t>
-  </si>
-  <si>
-    <t>13960-13979</t>
+    <t>110261-110280</t>
+  </si>
+  <si>
+    <t>111401-111420</t>
+  </si>
+  <si>
+    <t>113961-113980</t>
   </si>
   <si>
     <t>1097</t>
   </si>
   <si>
-    <t>14840-14859</t>
+    <t>114841-114860</t>
   </si>
   <si>
     <t>1098</t>
   </si>
   <si>
-    <t>15720-15739</t>
+    <t>115721-115740</t>
   </si>
   <si>
     <t>1099</t>
   </si>
   <si>
-    <t>380-399</t>
+    <t>100381-100400</t>
   </si>
   <si>
     <t>1100</t>
   </si>
   <si>
-    <t>660-679</t>
-  </si>
-  <si>
-    <t>2740-2759</t>
+    <t>100661-100680</t>
+  </si>
+  <si>
+    <t>102741-102760</t>
   </si>
   <si>
     <t>1101</t>
   </si>
   <si>
-    <t>3640-3659</t>
+    <t>103641-103660</t>
   </si>
   <si>
     <t>1102</t>
   </si>
   <si>
-    <t>3780-3799</t>
+    <t>103781-103800</t>
   </si>
   <si>
     <t>1103</t>
   </si>
   <si>
-    <t>4160-4179</t>
+    <t>104161-104180</t>
   </si>
   <si>
     <t>1104</t>
   </si>
   <si>
-    <t>4440-4459</t>
+    <t>104441-104460</t>
   </si>
   <si>
     <t>40 to 40</t>
@@ -2054,184 +2054,184 @@
     <t>1105</t>
   </si>
   <si>
-    <t>5860-5879</t>
+    <t>105861-105880</t>
   </si>
   <si>
     <t>1106</t>
   </si>
   <si>
-    <t>8860-8879</t>
+    <t>108861-108880</t>
   </si>
   <si>
     <t>1107</t>
   </si>
   <si>
-    <t>12420-12439</t>
+    <t>112421-112440</t>
   </si>
   <si>
     <t>1108</t>
   </si>
   <si>
-    <t>12680-12699</t>
+    <t>112681-112700</t>
   </si>
   <si>
     <t>1109</t>
   </si>
   <si>
-    <t>12940-12959</t>
+    <t>112941-112960</t>
   </si>
   <si>
     <t>1110</t>
   </si>
   <si>
-    <t>13080-13099</t>
-  </si>
-  <si>
-    <t>16380-16399</t>
-  </si>
-  <si>
-    <t>16520-16539</t>
-  </si>
-  <si>
-    <t>22680-22699</t>
+    <t>113081-113100</t>
+  </si>
+  <si>
+    <t>116381-116400</t>
+  </si>
+  <si>
+    <t>116521-116540</t>
+  </si>
+  <si>
+    <t>122681-122700</t>
   </si>
   <si>
     <t>1111</t>
   </si>
   <si>
-    <t>22940-22959</t>
+    <t>122941-122960</t>
   </si>
   <si>
     <t>1112</t>
   </si>
   <si>
-    <t>6520-6539</t>
-  </si>
-  <si>
-    <t>7920-7939</t>
+    <t>106521-106540</t>
+  </si>
+  <si>
+    <t>107921-107940</t>
   </si>
   <si>
     <t>1113</t>
   </si>
   <si>
-    <t>9000-9019</t>
+    <t>109001-109020</t>
   </si>
   <si>
     <t>1114</t>
   </si>
   <si>
-    <t>16800-16819</t>
+    <t>116801-116820</t>
   </si>
   <si>
     <t>1115</t>
   </si>
   <si>
-    <t>17560-17579</t>
+    <t>117561-117580</t>
   </si>
   <si>
     <t>1116</t>
   </si>
   <si>
-    <t>18460-18479</t>
+    <t>118461-118480</t>
   </si>
   <si>
     <t>1117</t>
   </si>
   <si>
-    <t>19220-19239</t>
+    <t>119221-119240</t>
   </si>
   <si>
     <t>1118</t>
   </si>
   <si>
-    <t>19840-19859</t>
+    <t>119841-119860</t>
   </si>
   <si>
     <t>1119</t>
   </si>
   <si>
-    <t>19980-19999</t>
+    <t>119981-120000</t>
   </si>
   <si>
     <t>1120</t>
   </si>
   <si>
-    <t>20860-20879</t>
+    <t>120861-120880</t>
   </si>
   <si>
     <t>1121</t>
   </si>
   <si>
-    <t>21360-21379</t>
+    <t>121361-121380</t>
   </si>
   <si>
     <t>1122</t>
   </si>
   <si>
-    <t>21640-21659</t>
+    <t>121641-121660</t>
   </si>
   <si>
     <t>1123</t>
   </si>
   <si>
-    <t>22280-22299</t>
+    <t>122281-122300</t>
   </si>
   <si>
     <t>1124</t>
   </si>
   <si>
-    <t>520-539</t>
-  </si>
-  <si>
-    <t>9640-9659</t>
+    <t>100521-100540</t>
+  </si>
+  <si>
+    <t>109641-109660</t>
   </si>
   <si>
     <t>1125</t>
   </si>
   <si>
-    <t>10640-10659</t>
-  </si>
-  <si>
-    <t>10780-10799</t>
-  </si>
-  <si>
-    <t>11540-11559</t>
-  </si>
-  <si>
-    <t>11920-11939</t>
+    <t>110641-110660</t>
+  </si>
+  <si>
+    <t>110781-110800</t>
+  </si>
+  <si>
+    <t>111541-111560</t>
+  </si>
+  <si>
+    <t>111921-111940</t>
   </si>
   <si>
     <t>1126</t>
   </si>
   <si>
-    <t>13460-13479</t>
+    <t>113461-113480</t>
   </si>
   <si>
     <t>1127</t>
   </si>
   <si>
-    <t>14580-14599</t>
+    <t>114581-114600</t>
   </si>
   <si>
     <t>1128</t>
   </si>
   <si>
-    <t>15100-15119</t>
-  </si>
-  <si>
-    <t>15980-15999</t>
+    <t>115101-115120</t>
+  </si>
+  <si>
+    <t>115981-116000</t>
   </si>
   <si>
     <t>1129</t>
   </si>
   <si>
-    <t>16120-16139</t>
+    <t>116121-116140</t>
   </si>
   <si>
     <t>1130</t>
   </si>
   <si>
-    <t>22420-22439</t>
+    <t>122421-122440</t>
   </si>
 </sst>
 </file>
@@ -2305,7 +2305,7 @@
     <col min="17" max="17" width="11.965397834777832" customWidth="1"/>
     <col min="18" max="18" width="9.140625" customWidth="1"/>
     <col min="19" max="19" width="9.140625" customWidth="1"/>
-    <col min="20" max="20" width="15.355362892150879" customWidth="1"/>
+    <col min="20" max="20" width="17.029979705810547" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
